--- a/pacjenci/HALINA JASIK.xlsx
+++ b/pacjenci/HALINA JASIK.xlsx
@@ -483,10 +483,14 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -523,7 +527,11 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -563,7 +571,11 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Do oceny</t>

--- a/pacjenci/HALINA JASIK.xlsx
+++ b/pacjenci/HALINA JASIK.xlsx
@@ -413,191 +413,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>14.11.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>chłoniak z komórek T/NK nieziarniczy; ocena zaawansowania choroby; od VIII 2022 narastające węzły chłonne obwodowe, aktualnie do 25 mm. Nie dostarczono do wglądu obrazów z poprzednich badań, w załączeniu jedynie opis TK z 7 XI 2022r.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono po 60 min od podania 18F-FDG. Glikemia: 81mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Pobudzone metabolicznie, powiększone i spakietowane węzły chłonne w zakresie wszystkich pięter szyi obustronnie na obszarze wielkości do około 44x22,5mm, SUV max do 2,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Bardzo liczne powiększone węzły chłonne wszystkich grup szyjnych, nieaktywne metabolicznie, częściowo spakietowane i w konglomeratach.    Klatka piersiowa i śródpiersie: Aktywne i pobudzone metabolicznie węzły chłonne śródpiersia: - otworu górnego klatki piersiowej (pogranicze grupy VI szyjnej i przednaczyniowej) po stronie prawej - konglomerat węzłów, największe wyodrębniające się śr. do 14 mm, SUVmax 3,0; - przytchawicze prawe górne oraz dolnej - spakietowane, o wym. do 27 x 25 x 47 mm, SUVmax do 3,5; - podostrogowe - spakietowane, wym. do 20 x 58 x 45 mm, SUVmax do 3,5; - wnękowe - po prawej śr. do 9 mm wg PET, SUVmax do 2,6; po lewej największy śr. do 22 mm, SUVmax do 4,4. Aktywne metabolicznie i pobudzone węzły chłonne podobojczykowe/przy przedniej ścianie klatki piersiowej: -  po prawej wielkości do 37 x 17 mm, SUVmax 2,7  - po lewej wielkości  do 22 x 12 mm, SUVmax do 2,0 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Miąższ płucny z obecnością skąpych zagęszczeń matowej szyb (częściowo mogą wynikać z mozaikowego upowietrzenia przy swobodnym oddychaniu podczas badania), zmiany niedodmowe płata środkowego płuca prawego. Obustronnie płyn w jamach opłucnowych, po prawej w wymiarze strzałkowym do 13 mm, po lewej ślad. Poszerzenie aorty wstępującej (śr. do 39-40 mm) do kontroli. Serce powiększone.  Brzuch i miednica: Pobudzony metaboliczne powiększony węzeł chłonny przy tetnicy biodrowej zewnętrznej po stronie lewej, średnicy 16 mm, SUVmax 3,0 [Im fuz 228]. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Splenomegalia, śledziona wym. do 136 x 101 x 140 mm, SI do 1920. Bardzo liczne powiększone do 25mm węzły chłonne okołoaortalne, przy tt biodrowych wspólnych, wewn i zewnętrznych. Zwapnienia w trzonie macicy.  Układ kostny: Niejednorodny wzmożony metabolizm FDG w obrębie struktur szkieletu osiowego, głównie odcinka L-S kręgosłupa i kościach miednicy, SUVmax do 3,6. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Uogólnione obniżenie densyjności kośćca. Stan po złamaniu kompresyjnym L1. Poziome ustawienie kości krzyżowej.  Wartości referencyjne: MBPS SUVmax 1,4. Prawy płat wątroby SUVmax do 2,2.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET-TK z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego po obu stronach przepony;  Poza tym jak w opisie.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>23.02.2023</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak z komórek T/NK nieziarniczy; ocena po 4 cyklach RCHOP.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 59 min od podania 18F-FDG. Glikemia: 99mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Asymetryczne pobudzenie metaboliczne w prawym płacie ciemieniowym - do ew. kontroli w badaniu MR.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie lewowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Poszerzenie aorty wstępującej (śr. do 40 mm) do kontroli. Węzły chłonne przytchawicze i przyaortalne wielkości do 12x9mm. Węzły chłonne pachowe obustronnie i międzypiersiowe lewe, wielkości do 16x10mm.  Śladowa ilość płynu w lewej jamie opłucnej. Drobne zmiany włókniste w szczytach obu płuc oraz obwodowo w płatach górnych obu płuc. Dość wydatne zmiany niedodmowo-naciekowo-włókniste nadprzeponowo w płucu lewym, z wysokim ustawieniem kopuły przepony. Niewielkie zmiany włókniste nadprzeponowo w płucu prawym.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona o wymiarach: 134x88x118mm. Ślad płynu okołowatrobowo. Drobne węzły chłonne okołoaortalne i przy naczyniach biodrowych. Drobne i wydatniejsze zwapnienia w trzonie macicy, najpewniej uwapnione mięśniaki, wielkości do 20x16mm. Niewielka ilość płynu w jamie Douglasa, zwłaszcza po stronie prawej.  Układ kostny: Aktywny metabolicznie obszar w topografii przedniego odcinka żebra IV po stronie prawej, SUV max 4,2 z niewielkim poszerzeniem obrysów tego żebra.  Niejednorodnie wzmożony metabolizm FDG w obrębie struktur szkieletu osiowego, głównie odcinka L-S kręgosłupa i w kościach miednicy, wyraźniej zwiększony w trzonach kręgowych: Th10, Th11, L1 i L3, SUV max 4,6-stan po złamaniach.  Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Uogólnione obniżenie densyjności kośćca. Dodatkowo stan po złamaniu kompresyjnym na poziomie Th12. Dyskopatie w odcinku szyjnym kręgosłupa. Ok. 10mm naczyniak w lewobocznej części trzonu Th6. Poziome ustawienie kości krzyżowej.  Inne: Pobudzenie metaboliczne w tkankach miękkich stawu barkowego prawego- czynnościowo?  Wartości referencyjne: MBPS SUVmax 1,7; Prawy płat wątroby SUVmax do 2,8.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET-TK z 18F-FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie.  Aktywny metabolicznie obszar w topografii przedniego odcinka żebra IV po stronie prawej, z niewielkim poszerzeniem obrysów tego żebra. Niejednorodny wzmożony metabolizm FDG w obrębie struktur szkieletu osiowego, głównie odcinka L-S kręgosłupa i w kościach miednicy - vide opis powyżej - do kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>4.6</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>20.06.2023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak z komórek T/NK nieziarniczy; ocena po 8 cyklach RCHOP.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 59 min od podania 18F-FDG. Glikemia: 98mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Asymetryczne pobudzenie metaboliczne w prawym płacie ciemieniowym - do ew. kontroli w badaniu MR.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie lewowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Poszerzenie aorty wstępującej (śr. do 40 mm) - do kontroli. Węzły chłonne przytchawicze i przyaortalne wielkości do 11x9mm. Węzły chłonne pachowe obustronnie i międzypiersiowe lewe, wielkości do 12x10mm.  Drobne zmiany włókniste w szczytach obu płuc oraz obwodowo w płatach górnych obu płuc. Ok. 5mm obwodowy guzek w segm. 1+2 płuca lewego. Dość wydatne zmiany niedodmowo-włókniste nadprzeponowo w płucu lewym, z wysokim ustawieniem kopuły przepony. Niewielkie zmiany włókniste nadprzeponowo w płucu prawym.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona o wymiarach: 123x77x118mm (poprzednio 134x88x118mm). Ślad płynu okołowątrobowo. Drobne węzły chłonne okołoaortalne i przy naczyniach biodrowych. Drobne i wydatniejsze zwapnienia w trzonie macicy, najpewniej uwapnione mięśniaki, wielkości do 20x16mm. Niewielka ilość płynu w jamie Douglasa po stronie lewej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Cechy uogólnionego zaniku kostnego. Wielopoziomowo włamania blaszek granicznych z obniżeniem wysokości trzonów kręgowych, zwłaszcza Th3, Th8, Th10 i Th11 oraz wszystkie trzony lędźwiowe. Stan po złamaniu kompresyjnym trzonu Th12, ze znacznym obniżeniem wysokości trzonu. Dyskopatie w odcinku szyjnym kręgosłupa. Ok. 10mm naczyniak w lewobocznej części trzonu Th6. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Poziome ustawienie kości krzyżowej.   Wartości referencyjne: MBPS SUVmax 2,0; Prawy płat wątroby SUVmax do 3,0.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET-TK z 18F-FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>3</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/HALINA JASIK.xlsx
+++ b/pacjenci/HALINA JASIK.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono po 60 min od podania 18F-FDG. Glikemia: 81mg%.</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Pobudzone metabolicznie, powiększone i spakietowane węzły chłonne w zakresie wszystkich pięter szyi obustronnie na obszarze wielkości do około 44x22,5mm, SUV max do 2,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Bardzo liczne powiększone węzły chłonne wszystkich grup szyjnych, nieaktywne metabolicznie, częściowo spakietowane i w konglomeratach.    Klatka piersiowa i śródpiersie: Aktywne i pobudzone metabolicznie węzły chłonne śródpiersia: - otworu górnego klatki piersiowej (pogranicze grupy VI szyjnej i przednaczyniowej) po stronie prawej - konglomerat węzłów, największe wyodrębniające się śr. do 14 mm, SUVmax 3,0; - przytchawicze prawe górne oraz dolnej - spakietowane, o wym. do 27 x 25 x 47 mm, SUVmax do 3,5; - podostrogowe - spakietowane, wym. do 20 x 58 x 45 mm, SUVmax do 3,5; - wnękowe - po prawej śr. do 9 mm wg PET, SUVmax do 2,6; po lewej największy śr. do 22 mm, SUVmax do 4,4. Aktywne metabolicznie i pobudzone węzły chłonne podobojczykowe/przy przedniej ścianie klatki piersiowej: -  po prawej wielkości do 37 x 17 mm, SUVmax 2,7  - po lewej wielkości  do 22 x 12 mm, SUVmax do 2,0 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Miąższ płucny z obecnością skąpych zagęszczeń matowej szyb (częściowo mogą wynikać z mozaikowego upowietrzenia przy swobodnym oddychaniu podczas badania), zmiany niedodmowe płata środkowego płuca prawego. Obustronnie płyn w jamach opłucnowych, po prawej w wymiarze strzałkowym do 13 mm, po lewej ślad. Poszerzenie aorty wstępującej (śr. do 39-40 mm) do kontroli. Serce powiększone.  Brzuch i miednica: Pobudzony metaboliczne powiększony węzeł chłonny przy tetnicy biodrowej zewnętrznej po stronie lewej, średnicy 16 mm, SUVmax 3,0 [Im fuz 228]. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Splenomegalia, śledziona wym. do 136 x 101 x 140 mm, SI do 1920. Bardzo liczne powiększone do 25mm węzły chłonne okołoaortalne, przy tt biodrowych wspólnych, wewn i zewnętrznych. Zwapnienia w trzonie macicy.  Układ kostny: Niejednorodny wzmożony metabolizm FDG w obrębie struktur szkieletu osiowego, głównie odcinka L-S kręgosłupa i kościach miednicy, SUVmax do 3,6. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Uogólnione obniżenie densyjności kośćca. Stan po złamaniu kompresyjnym L1. Poziome ustawienie kości krzyżowej.  Wartości referencyjne: MBPS SUVmax 1,4. Prawy płat wątroby SUVmax do 2,2.</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Pobudzone metabolicznie, powiększone i spakietowane węzły chłonne w zakresie wszystkich pięter szyi obustronnie na obszarze wielkości do około 44x22,5mm, SUV max do 2,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Bardzo liczne powiększone węzły chłonne wszystkich grup szyjnych, nieaktywne metabolicznie, częściowo spakietowane i w konglomeratach.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne i pobudzone metabolicznie węzły chłonne śródpiersia: - otworu górnego klatki piersiowej (pogranicze grupy VI szyjnej i przednaczyniowej) po stronie prawej - konglomerat węzłów, największe wyodrębniające się śr. do 14 mm, SUVmax 3,0; - przytchawicze prawe górne oraz dolnej - spakietowane, o wym. do 27 x 25 x 47 mm, SUVmax do 3,5; - podostrogowe - spakietowane, wym. do 20 x 58 x 45 mm, SUVmax do 3,5; - wnękowe - po prawej śr. do 9 mm wg PET, SUVmax do 2,6; po lewej największy śr. do 22 mm, SUVmax do 4,4. Aktywne metabolicznie i pobudzone węzły chłonne podobojczykowe/przy przedniej ścianie klatki piersiowej: -  po prawej wielkości do 37 x 17 mm, SUVmax 2,7  - po lewej wielkości  do 22 x 12 mm, SUVmax do 2,0 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Miąższ płucny z obecnością skąpych zagęszczeń matowej szyb (częściowo mogą wynikać z mozaikowego upowietrzenia przy swobodnym oddychaniu podczas badania), zmiany niedodmowe płata środkowego płuca prawego. Obustronnie płyn w jamach opłucnowych, po prawej w wymiarze strzałkowym do 13 mm, po lewej ślad. Poszerzenie aorty wstępującej (śr. do 39-40 mm) do kontroli. Serce powiększone.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pobudzony metaboliczne powiększony węzeł chłonny przy tetnicy biodrowej zewnętrznej po stronie lewej, średnicy 16 mm, SUVmax 3,0 [Im fuz 228]. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Splenomegalia, śledziona wym. do 136 x 101 x 140 mm, SI do 1920. Bardzo liczne powiększone do 25mm węzły chłonne okołoaortalne, przy tt biodrowych wspólnych, wewn i zewnętrznych. Zwapnienia w trzonie macicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Niejednorodny wzmożony metabolizm FDG w obrębie struktur szkieletu osiowego, głównie odcinka L-S kręgosłupa i kościach miednicy, SUVmax do 3,6. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Uogólnione obniżenie densyjności kośćca. Stan po złamaniu kompresyjnym L1. Poziome ustawienie kości krzyżowej.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET-TK z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego po obu stronach przepony;  Poza tym jak w opisie.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>4.4</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 59 min od podania 18F-FDG. Glikemia: 99mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Asymetryczne pobudzenie metaboliczne w prawym płacie ciemieniowym - do ew. kontroli w badaniu MR.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie lewowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Poszerzenie aorty wstępującej (śr. do 40 mm) do kontroli. Węzły chłonne przytchawicze i przyaortalne wielkości do 12x9mm. Węzły chłonne pachowe obustronnie i międzypiersiowe lewe, wielkości do 16x10mm.  Śladowa ilość płynu w lewej jamie opłucnej. Drobne zmiany włókniste w szczytach obu płuc oraz obwodowo w płatach górnych obu płuc. Dość wydatne zmiany niedodmowo-naciekowo-włókniste nadprzeponowo w płucu lewym, z wysokim ustawieniem kopuły przepony. Niewielkie zmiany włókniste nadprzeponowo w płucu prawym.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona o wymiarach: 134x88x118mm. Ślad płynu okołowatrobowo. Drobne węzły chłonne okołoaortalne i przy naczyniach biodrowych. Drobne i wydatniejsze zwapnienia w trzonie macicy, najpewniej uwapnione mięśniaki, wielkości do 20x16mm. Niewielka ilość płynu w jamie Douglasa, zwłaszcza po stronie prawej.  Układ kostny: Aktywny metabolicznie obszar w topografii przedniego odcinka żebra IV po stronie prawej, SUV max 4,2 z niewielkim poszerzeniem obrysów tego żebra.  Niejednorodnie wzmożony metabolizm FDG w obrębie struktur szkieletu osiowego, głównie odcinka L-S kręgosłupa i w kościach miednicy, wyraźniej zwiększony w trzonach kręgowych: Th10, Th11, L1 i L3, SUV max 4,6-stan po złamaniach.  Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Uogólnione obniżenie densyjności kośćca. Dodatkowo stan po złamaniu kompresyjnym na poziomie Th12. Dyskopatie w odcinku szyjnym kręgosłupa. Ok. 10mm naczyniak w lewobocznej części trzonu Th6. Poziome ustawienie kości krzyżowej.  Inne: Pobudzenie metaboliczne w tkankach miękkich stawu barkowego prawego- czynnościowo?  Wartości referencyjne: MBPS SUVmax 1,7; Prawy płat wątroby SUVmax do 2,8.</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Asymetryczne pobudzenie metaboliczne w prawym płacie ciemieniowym - do ew. kontroli w badaniu MR.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie lewowypukłe skrzywienie przegrody nosowej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Poszerzenie aorty wstępującej (śr. do 40 mm) do kontroli. Węzły chłonne przytchawicze i przyaortalne wielkości do 12x9mm. Węzły chłonne pachowe obustronnie i międzypiersiowe lewe, wielkości do 16x10mm.  Śladowa ilość płynu w lewej jamie opłucnej. Drobne zmiany włókniste w szczytach obu płuc oraz obwodowo w płatach górnych obu płuc. Dość wydatne zmiany niedodmowo-naciekowo-włókniste nadprzeponowo w płucu lewym, z wysokim ustawieniem kopuły przepony. Niewielkie zmiany włókniste nadprzeponowo w płucu prawym.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona o wymiarach: 134x88x118mm. Ślad płynu okołowatrobowo. Drobne węzły chłonne okołoaortalne i przy naczyniach biodrowych. Drobne i wydatniejsze zwapnienia w trzonie macicy, najpewniej uwapnione mięśniaki, wielkości do 20x16mm. Niewielka ilość płynu w jamie Douglasa, zwłaszcza po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w topografii przedniego odcinka żebra IV po stronie prawej, SUV max 4,2 z niewielkim poszerzeniem obrysów tego żebra.  Niejednorodnie wzmożony metabolizm FDG w obrębie struktur szkieletu osiowego, głównie odcinka L-S kręgosłupa i w kościach miednicy, wyraźniej zwiększony w trzonach kręgowych: Th10, Th11, L1 i L3, SUV max 4,6-stan po złamaniach.  Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Uogólnione obniżenie densyjności kośćca. Dodatkowo stan po złamaniu kompresyjnym na poziomie Th12. Dyskopatie w odcinku szyjnym kręgosłupa. Ok. 10mm naczyniak w lewobocznej części trzonu Th6. Poziome ustawienie kości krzyżowej.  Inne: Pobudzenie metaboliczne w tkankach miękkich stawu barkowego prawego- czynnościowo?</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET-TK z 18F-FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie.  Aktywny metabolicznie obszar w topografii przedniego odcinka żebra IV po stronie prawej, z niewielkim poszerzeniem obrysów tego żebra. Niejednorodny wzmożony metabolizm FDG w obrębie struktur szkieletu osiowego, głównie odcinka L-S kręgosłupa i w kościach miednicy - vide opis powyżej - do kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>4.6</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 59 min od podania 18F-FDG. Glikemia: 98mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Asymetryczne pobudzenie metaboliczne w prawym płacie ciemieniowym - do ew. kontroli w badaniu MR.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie lewowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Poszerzenie aorty wstępującej (śr. do 40 mm) - do kontroli. Węzły chłonne przytchawicze i przyaortalne wielkości do 11x9mm. Węzły chłonne pachowe obustronnie i międzypiersiowe lewe, wielkości do 12x10mm.  Drobne zmiany włókniste w szczytach obu płuc oraz obwodowo w płatach górnych obu płuc. Ok. 5mm obwodowy guzek w segm. 1+2 płuca lewego. Dość wydatne zmiany niedodmowo-włókniste nadprzeponowo w płucu lewym, z wysokim ustawieniem kopuły przepony. Niewielkie zmiany włókniste nadprzeponowo w płucu prawym.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona o wymiarach: 123x77x118mm (poprzednio 134x88x118mm). Ślad płynu okołowątrobowo. Drobne węzły chłonne okołoaortalne i przy naczyniach biodrowych. Drobne i wydatniejsze zwapnienia w trzonie macicy, najpewniej uwapnione mięśniaki, wielkości do 20x16mm. Niewielka ilość płynu w jamie Douglasa po stronie lewej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Cechy uogólnionego zaniku kostnego. Wielopoziomowo włamania blaszek granicznych z obniżeniem wysokości trzonów kręgowych, zwłaszcza Th3, Th8, Th10 i Th11 oraz wszystkie trzony lędźwiowe. Stan po złamaniu kompresyjnym trzonu Th12, ze znacznym obniżeniem wysokości trzonu. Dyskopatie w odcinku szyjnym kręgosłupa. Ok. 10mm naczyniak w lewobocznej części trzonu Th6. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Poziome ustawienie kości krzyżowej.   Wartości referencyjne: MBPS SUVmax 2,0; Prawy płat wątroby SUVmax do 3,0.</t>
+          <t>98</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Asymetryczne pobudzenie metaboliczne w prawym płacie ciemieniowym - do ew. kontroli w badaniu MR.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie lewowypukłe skrzywienie przegrody nosowej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Poszerzenie aorty wstępującej (śr. do 40 mm) - do kontroli. Węzły chłonne przytchawicze i przyaortalne wielkości do 11x9mm. Węzły chłonne pachowe obustronnie i międzypiersiowe lewe, wielkości do 12x10mm.  Drobne zmiany włókniste w szczytach obu płuc oraz obwodowo w płatach górnych obu płuc. Ok. 5mm obwodowy guzek w segm. 1+2 płuca lewego. Dość wydatne zmiany niedodmowo-włókniste nadprzeponowo w płucu lewym, z wysokim ustawieniem kopuły przepony. Niewielkie zmiany włókniste nadprzeponowo w płucu prawym.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona o wymiarach: 123x77x118mm (poprzednio 134x88x118mm). Ślad płynu okołowątrobowo. Drobne węzły chłonne okołoaortalne i przy naczyniach biodrowych. Drobne i wydatniejsze zwapnienia w trzonie macicy, najpewniej uwapnione mięśniaki, wielkości do 20x16mm. Niewielka ilość płynu w jamie Douglasa po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Cechy uogólnionego zaniku kostnego. Wielopoziomowo włamania blaszek granicznych z obniżeniem wysokości trzonów kręgowych, zwłaszcza Th3, Th8, Th10 i Th11 oraz wszystkie trzony lędźwiowe. Stan po złamaniu kompresyjnym trzonu Th12, ze znacznym obniżeniem wysokości trzonu. Dyskopatie w odcinku szyjnym kręgosłupa. Ok. 10mm naczyniak w lewobocznej części trzonu Th6. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Poziome ustawienie kości krzyżowej.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET-TK z 18F-FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>3</v>
       </c>
     </row>
